--- a/Orçado/Orça-Despesas Administrativas/Marketing Interno.xlsx
+++ b/Orçado/Orça-Despesas Administrativas/Marketing Interno.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\henrique.santos\orcamento2027\budgetflow-insights\Orçado\Orça-Despesas Administrativas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{408D306C-1399-47CE-A5E2-23B368BD88A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7754848A-A434-4C42-B643-43B9690684BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{03608223-CCBA-4037-A9F0-BF57F4300B6F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6659E8E9-9810-44F6-A60D-3DD9830A4818}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,28 +39,128 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="35">
+  <si>
+    <t>GRUPO_CONTABIL</t>
+  </si>
+  <si>
+    <t>CONTA_CONTABIL</t>
+  </si>
+  <si>
+    <t>Descrição C. Contábil</t>
+  </si>
+  <si>
+    <t>3.4.01.01-CUSTO DE PESSOAL</t>
+  </si>
+  <si>
+    <t>3.4.01.01.0001</t>
+  </si>
+  <si>
+    <t>Custo de Pessoal</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Honorários Diretoria</t>
+  </si>
   <si>
     <t>3.4.01.02-SERVICOS DE TERCEIROS</t>
   </si>
   <si>
+    <t>3.4.01.02.0002</t>
+  </si>
+  <si>
+    <t>Serviços de Terceiros</t>
+  </si>
+  <si>
     <t>3.4.01.10-OUTRAS DESPESAS ADMINISTRATIVAS</t>
   </si>
   <si>
-    <t>3.4.01.05-DEPRECIACOES, EXAUSTOES E AMORTIZACOES</t>
-  </si>
-  <si>
-    <t>3.4.01.04-MANUTENCAO E CONSERVACAO DE BENS</t>
-  </si>
-  <si>
-    <t>GRUPO_CONTABIL</t>
+    <t>3.4.01.10.0020</t>
+  </si>
+  <si>
+    <t>Outras Despesas Administrativas</t>
+  </si>
+  <si>
+    <t>3.4.01.10.0003</t>
+  </si>
+  <si>
+    <t>Contribuições e Doações</t>
+  </si>
+  <si>
+    <t>3.4.01.07-UTILIDADES E SERVICOS</t>
+  </si>
+  <si>
+    <t>3.4.01.07.0002</t>
+  </si>
+  <si>
+    <t>Telefone</t>
+  </si>
+  <si>
+    <t>3.4.01.10.0053</t>
+  </si>
+  <si>
+    <t>Rateio de Veículos</t>
+  </si>
+  <si>
+    <t>3.4.01.05-DEPRECIACOES, EXAUSTOES E AMORTIZAÇÕES</t>
+  </si>
+  <si>
+    <t>3.4.01.05.0001</t>
+  </si>
+  <si>
+    <t>Depreciações</t>
+  </si>
+  <si>
+    <t>Utilidades e serviços</t>
+  </si>
+  <si>
+    <t>3.4.02.01.0010</t>
+  </si>
+  <si>
+    <t>Plano de Saúde</t>
+  </si>
+  <si>
+    <t>Plano de Previdência Privada - Sócios</t>
+  </si>
+  <si>
+    <t>3.4.01.04 888 MANUTENCAO E CONSERVACAO DE BENS</t>
+  </si>
+  <si>
+    <t>3.4.01.04.0002</t>
+  </si>
+  <si>
+    <t>Peças, Acessórios e Materiais</t>
+  </si>
+  <si>
+    <t>3.4.01.04.0004</t>
+  </si>
+  <si>
+    <t>Impressos e Materiais de Expediente</t>
+  </si>
+  <si>
+    <t>3.4.01.04.0005</t>
+  </si>
+  <si>
+    <t>Materiais para Manutenção e Conservação</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -82,20 +182,44 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -114,20 +238,57 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="17" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{84D9D5A2-C574-474E-861A-2438B2BE8A4D}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{D9A2F797-3357-43EB-B7EB-EB33AF1ED0C7}"/>
+    <cellStyle name="Vírgula 3" xfId="3" xr:uid="{D82946F7-AB91-4B26-A43D-A58184D06C46}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -458,297 +619,718 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50EFBC29-7E2B-422D-A753-57294899EC1C}">
-  <dimension ref="A1:M7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FFBCCEF-DFDA-4BAE-9725-786A68696FAC}">
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="15" width="10.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E1" s="3">
+        <v>46143</v>
+      </c>
+      <c r="F1" s="3">
+        <v>46174</v>
+      </c>
+      <c r="G1" s="3">
+        <v>46204</v>
+      </c>
+      <c r="H1" s="3">
+        <v>46235</v>
+      </c>
+      <c r="I1" s="3">
+        <v>46266</v>
+      </c>
+      <c r="J1" s="3">
+        <v>46296</v>
+      </c>
+      <c r="K1" s="3">
+        <v>46327</v>
+      </c>
+      <c r="L1" s="3">
+        <v>46357</v>
+      </c>
+      <c r="M1" s="3">
+        <v>46388</v>
+      </c>
+      <c r="N1" s="3">
+        <v>46419</v>
+      </c>
+      <c r="O1" s="3">
+        <v>46447</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1">
-        <v>46113</v>
-      </c>
-      <c r="C1" s="1">
-        <v>46143</v>
-      </c>
-      <c r="D1" s="1">
-        <v>46174</v>
-      </c>
-      <c r="E1" s="1">
-        <v>46204</v>
-      </c>
-      <c r="F1" s="1">
-        <v>46235</v>
-      </c>
-      <c r="G1" s="1">
-        <v>46266</v>
-      </c>
-      <c r="H1" s="1">
-        <v>46296</v>
-      </c>
-      <c r="I1" s="1">
-        <v>46327</v>
-      </c>
-      <c r="J1" s="1">
-        <v>46357</v>
-      </c>
-      <c r="K1" s="1">
-        <v>46388</v>
-      </c>
-      <c r="L1" s="1">
-        <v>46419</v>
-      </c>
-      <c r="M1" s="1">
-        <v>46447</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2">
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0</v>
+      </c>
+      <c r="L2" s="4">
+        <v>0</v>
+      </c>
+      <c r="M2" s="4">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4">
+        <v>0</v>
+      </c>
+      <c r="O2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="6">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6">
+        <v>0</v>
+      </c>
+      <c r="F3" s="6">
+        <v>0</v>
+      </c>
+      <c r="G3" s="6">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6">
+        <v>0</v>
+      </c>
+      <c r="I3" s="6">
+        <v>0</v>
+      </c>
+      <c r="J3" s="6">
+        <v>0</v>
+      </c>
+      <c r="K3" s="6">
+        <v>0</v>
+      </c>
+      <c r="L3" s="6">
+        <v>0</v>
+      </c>
+      <c r="M3" s="6">
+        <v>0</v>
+      </c>
+      <c r="N3" s="6">
+        <v>0</v>
+      </c>
+      <c r="O3" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="6">
         <v>5549.9</v>
       </c>
-      <c r="C2" s="2">
+      <c r="E4" s="6">
         <v>5784.8</v>
       </c>
-      <c r="D2" s="2">
+      <c r="F4" s="6">
         <v>5839.8</v>
       </c>
-      <c r="E2" s="2">
+      <c r="G4" s="6">
         <v>5549.9</v>
       </c>
-      <c r="F2" s="2">
+      <c r="H4" s="6">
         <v>5549.9</v>
       </c>
-      <c r="G2" s="2">
+      <c r="I4" s="6">
         <v>5549.9</v>
       </c>
-      <c r="H2" s="2">
+      <c r="J4" s="6">
         <v>5549.9</v>
       </c>
-      <c r="I2" s="2">
+      <c r="K4" s="6">
         <v>5549.9</v>
       </c>
-      <c r="J2" s="2">
+      <c r="L4" s="6">
         <v>5549.9</v>
       </c>
-      <c r="K2" s="2">
+      <c r="M4" s="6">
         <v>5549.9</v>
       </c>
-      <c r="L2" s="2">
+      <c r="N4" s="6">
         <v>5549.9</v>
       </c>
-      <c r="M2" s="2">
+      <c r="O4" s="6">
         <v>5549.9</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="6">
         <v>200</v>
       </c>
-      <c r="C3" s="2">
+      <c r="E5" s="6">
         <v>30</v>
       </c>
-      <c r="D3" s="2">
+      <c r="F5" s="6">
         <v>30</v>
       </c>
-      <c r="E3" s="2">
+      <c r="G5" s="6">
         <v>30</v>
       </c>
-      <c r="F3" s="2">
+      <c r="H5" s="6">
         <v>30</v>
       </c>
-      <c r="G3" s="2">
+      <c r="I5" s="6">
         <v>30</v>
       </c>
-      <c r="H3" s="2">
+      <c r="J5" s="6">
         <v>30</v>
       </c>
-      <c r="I3" s="2">
+      <c r="K5" s="6">
         <v>30</v>
       </c>
-      <c r="J3" s="2">
+      <c r="L5" s="6">
         <v>30</v>
       </c>
-      <c r="K3" s="2">
+      <c r="M5" s="6">
         <v>30</v>
       </c>
-      <c r="L3" s="2">
+      <c r="N5" s="6">
         <v>30</v>
       </c>
-      <c r="M3" s="2">
+      <c r="O5" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="6">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0</v>
+      </c>
+      <c r="I6" s="6">
+        <v>0</v>
+      </c>
+      <c r="J6" s="6">
+        <v>0</v>
+      </c>
+      <c r="K6" s="6">
+        <v>0</v>
+      </c>
+      <c r="L6" s="6">
+        <v>0</v>
+      </c>
+      <c r="M6" s="6">
+        <v>0</v>
+      </c>
+      <c r="N6" s="6">
+        <v>0</v>
+      </c>
+      <c r="O6" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0</v>
+      </c>
+      <c r="I7" s="6">
+        <v>0</v>
+      </c>
+      <c r="J7" s="6">
+        <v>0</v>
+      </c>
+      <c r="K7" s="6">
+        <v>0</v>
+      </c>
+      <c r="L7" s="6">
+        <v>0</v>
+      </c>
+      <c r="M7" s="6">
+        <v>0</v>
+      </c>
+      <c r="N7" s="6">
+        <v>0</v>
+      </c>
+      <c r="O7" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0</v>
+      </c>
+      <c r="I8" s="6">
+        <v>0</v>
+      </c>
+      <c r="J8" s="6">
+        <v>0</v>
+      </c>
+      <c r="K8" s="6">
+        <v>0</v>
+      </c>
+      <c r="L8" s="6">
+        <v>0</v>
+      </c>
+      <c r="M8" s="6">
+        <v>0</v>
+      </c>
+      <c r="N8" s="6">
+        <v>0</v>
+      </c>
+      <c r="O8" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="6">
         <v>100</v>
       </c>
-      <c r="C4" s="2">
+      <c r="E9" s="6">
         <v>100</v>
       </c>
-      <c r="D4" s="2">
+      <c r="F9" s="6">
         <v>100</v>
       </c>
-      <c r="E4" s="2">
+      <c r="G9" s="6">
         <v>100</v>
       </c>
-      <c r="F4" s="2">
+      <c r="H9" s="6">
         <v>100</v>
       </c>
-      <c r="G4" s="2">
+      <c r="I9" s="6">
         <v>100</v>
       </c>
-      <c r="H4" s="2">
+      <c r="J9" s="6">
         <v>100</v>
       </c>
-      <c r="I4" s="2">
+      <c r="K9" s="6">
         <v>100</v>
       </c>
-      <c r="J4" s="2">
+      <c r="L9" s="6">
         <v>100</v>
       </c>
-      <c r="K4" s="2">
+      <c r="M9" s="6">
         <v>100</v>
       </c>
-      <c r="L4" s="2">
+      <c r="N9" s="6">
         <v>100</v>
       </c>
-      <c r="M4" s="2">
+      <c r="O9" s="6">
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6">
+        <v>0</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6">
+        <v>0</v>
+      </c>
+      <c r="I10" s="6">
+        <v>0</v>
+      </c>
+      <c r="J10" s="6">
+        <v>0</v>
+      </c>
+      <c r="K10" s="6">
+        <v>0</v>
+      </c>
+      <c r="L10" s="6">
+        <v>0</v>
+      </c>
+      <c r="M10" s="6">
+        <v>0</v>
+      </c>
+      <c r="N10" s="6">
+        <v>0</v>
+      </c>
+      <c r="O10" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6">
+        <v>0</v>
+      </c>
+      <c r="I11" s="6">
+        <v>0</v>
+      </c>
+      <c r="J11" s="6">
+        <v>0</v>
+      </c>
+      <c r="K11" s="6">
+        <v>0</v>
+      </c>
+      <c r="L11" s="6">
+        <v>0</v>
+      </c>
+      <c r="M11" s="6">
+        <v>0</v>
+      </c>
+      <c r="N11" s="6">
+        <v>0</v>
+      </c>
+      <c r="O11" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="6">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6">
+        <v>0</v>
+      </c>
+      <c r="I12" s="6">
+        <v>0</v>
+      </c>
+      <c r="J12" s="6">
+        <v>0</v>
+      </c>
+      <c r="K12" s="6">
+        <v>0</v>
+      </c>
+      <c r="L12" s="6">
+        <v>0</v>
+      </c>
+      <c r="M12" s="6">
+        <v>0</v>
+      </c>
+      <c r="N12" s="6">
+        <v>0</v>
+      </c>
+      <c r="O12" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="6">
         <v>800</v>
       </c>
-      <c r="C5" s="2">
+      <c r="E13" s="6">
         <v>700</v>
       </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2">
-        <v>0</v>
-      </c>
-      <c r="K5" s="2">
-        <v>0</v>
-      </c>
-      <c r="L5" s="2">
-        <v>0</v>
-      </c>
-      <c r="M5" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="2">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2">
-        <v>5</v>
-      </c>
-      <c r="D6" s="2">
-        <v>5</v>
-      </c>
-      <c r="E6" s="2">
-        <v>5</v>
-      </c>
-      <c r="F6" s="2">
-        <v>5</v>
-      </c>
-      <c r="G6" s="2">
-        <v>5</v>
-      </c>
-      <c r="H6" s="2">
-        <v>5</v>
-      </c>
-      <c r="I6" s="2">
-        <v>5</v>
-      </c>
-      <c r="J6" s="2">
-        <v>5</v>
-      </c>
-      <c r="K6" s="2">
-        <v>5</v>
-      </c>
-      <c r="L6" s="2">
-        <v>5</v>
-      </c>
-      <c r="M6" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="2">
-        <v>5</v>
-      </c>
-      <c r="C7" s="2">
-        <v>5</v>
-      </c>
-      <c r="D7" s="2">
-        <v>5</v>
-      </c>
-      <c r="E7" s="2">
-        <v>5</v>
-      </c>
-      <c r="F7" s="2">
-        <v>5</v>
-      </c>
-      <c r="G7" s="2">
-        <v>5</v>
-      </c>
-      <c r="H7" s="2">
-        <v>5</v>
-      </c>
-      <c r="I7" s="2">
-        <v>5</v>
-      </c>
-      <c r="J7" s="2">
-        <v>5</v>
-      </c>
-      <c r="K7" s="2">
-        <v>5</v>
-      </c>
-      <c r="L7" s="2">
-        <v>5</v>
-      </c>
-      <c r="M7" s="2">
+      <c r="F13" s="6">
+        <v>0</v>
+      </c>
+      <c r="G13" s="6">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6">
+        <v>0</v>
+      </c>
+      <c r="I13" s="6">
+        <v>0</v>
+      </c>
+      <c r="J13" s="6">
+        <v>0</v>
+      </c>
+      <c r="K13" s="6">
+        <v>0</v>
+      </c>
+      <c r="L13" s="6">
+        <v>0</v>
+      </c>
+      <c r="M13" s="6">
+        <v>0</v>
+      </c>
+      <c r="N13" s="6">
+        <v>0</v>
+      </c>
+      <c r="O13" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="6">
+        <v>5</v>
+      </c>
+      <c r="E14" s="6">
+        <v>5</v>
+      </c>
+      <c r="F14" s="6">
+        <v>5</v>
+      </c>
+      <c r="G14" s="6">
+        <v>5</v>
+      </c>
+      <c r="H14" s="6">
+        <v>5</v>
+      </c>
+      <c r="I14" s="6">
+        <v>5</v>
+      </c>
+      <c r="J14" s="6">
+        <v>5</v>
+      </c>
+      <c r="K14" s="6">
+        <v>5</v>
+      </c>
+      <c r="L14" s="6">
+        <v>5</v>
+      </c>
+      <c r="M14" s="6">
+        <v>5</v>
+      </c>
+      <c r="N14" s="6">
+        <v>5</v>
+      </c>
+      <c r="O14" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="6">
+        <v>5</v>
+      </c>
+      <c r="E15" s="6">
+        <v>5</v>
+      </c>
+      <c r="F15" s="6">
+        <v>5</v>
+      </c>
+      <c r="G15" s="6">
+        <v>5</v>
+      </c>
+      <c r="H15" s="6">
+        <v>5</v>
+      </c>
+      <c r="I15" s="6">
+        <v>5</v>
+      </c>
+      <c r="J15" s="6">
+        <v>5</v>
+      </c>
+      <c r="K15" s="6">
+        <v>5</v>
+      </c>
+      <c r="L15" s="6">
+        <v>5</v>
+      </c>
+      <c r="M15" s="6">
+        <v>5</v>
+      </c>
+      <c r="N15" s="6">
+        <v>5</v>
+      </c>
+      <c r="O15" s="6">
         <v>5</v>
       </c>
     </row>
